--- a/public/docs/agentpm-migration-plan.xlsx
+++ b/public/docs/agentpm-migration-plan.xlsx
@@ -690,7 +690,7 @@
       <c r="E12" s="6" t="n"/>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>まず3〜5人で。全員を一度に入れない</t>
+          <t>無料プランは5名まで。まず3〜5人で</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       <c r="E15" s="6" t="n"/>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>既定は見せない設定です</t>
+          <t>はじめは見せない設定です</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       <c r="E16" s="6" t="n"/>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>「URLを開けば進捗が見えます」で足ります</t>
+          <t>「招待メールから入れば進捗が見えます」で足ります</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       <c r="E18" s="6" t="n"/>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>グループに招いて合言葉を入れるだけ</t>
+          <t>無料プランは3グループまで</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       <c r="E19" s="6" t="n"/>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>毎時まとめて／メンション時のみ／取り込まない</t>
+          <t>毎時まとめて／メンション時のみ（即時）／取り込まない</t>
         </is>
       </c>
     </row>
